--- a/output/details/2026-05-08/preprocessed_data.xlsx
+++ b/output/details/2026-05-08/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46150</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1079780984055465</v>
+        <v>-0.1075103366613583</v>
       </c>
       <c r="C2" t="n">
-        <v>0.204114986374662</v>
+        <v>-0.1321931670297761</v>
       </c>
       <c r="D2" t="n">
-        <v>0.203819600722065</v>
+        <v>-0.1319301314504558</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1339405214766684</v>
+        <v>0.01600333265753751</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001703777199340912</v>
+        <v>0.001704143012428022</v>
       </c>
       <c r="G2" t="n">
-        <v>1.771032488237568</v>
+        <v>2.354591981537806</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4634137977365982</v>
+        <v>-0.2565322433169212</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
